--- a/artfynd/A 57857-2025 artfynd.xlsx
+++ b/artfynd/A 57857-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>134215444</v>
       </c>
       <c r="B3" t="n">
-        <v>91953</v>
+        <v>91955</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 57857-2025 artfynd.xlsx
+++ b/artfynd/A 57857-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134215431</v>
+        <v>134215444</v>
       </c>
       <c r="B2" t="n">
-        <v>57975</v>
+        <v>91956</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>469217</v>
+        <v>469509</v>
       </c>
       <c r="R2" t="n">
-        <v>7034380</v>
+        <v>7034257</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134215444</v>
+        <v>134215431</v>
       </c>
       <c r="B3" t="n">
-        <v>91956</v>
+        <v>57975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469509</v>
+        <v>469217</v>
       </c>
       <c r="R3" t="n">
-        <v>7034257</v>
+        <v>7034380</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 57857-2025 artfynd.xlsx
+++ b/artfynd/A 57857-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134215444</v>
       </c>
       <c r="B2" t="n">
-        <v>91956</v>
+        <v>91963</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 57857-2025 artfynd.xlsx
+++ b/artfynd/A 57857-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134215444</v>
       </c>
       <c r="B2" t="n">
-        <v>91963</v>
+        <v>91970</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134215431</v>
+        <v>134215423</v>
       </c>
       <c r="B3" t="n">
         <v>57975</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469217</v>
+        <v>469386</v>
       </c>
       <c r="R3" t="n">
-        <v>7034380</v>
+        <v>7034241</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,7 +874,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134215433</v>
+        <v>134215424</v>
       </c>
       <c r="B4" t="n">
         <v>57975</v>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469220</v>
+        <v>469429</v>
       </c>
       <c r="R4" t="n">
-        <v>7034360</v>
+        <v>7034272</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1078,7 +1078,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134215424</v>
+        <v>134215426</v>
       </c>
       <c r="B6" t="n">
         <v>57975</v>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>469429</v>
+        <v>469459</v>
       </c>
       <c r="R6" t="n">
-        <v>7034272</v>
+        <v>7034328</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,7 +1180,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134215426</v>
+        <v>134215427</v>
       </c>
       <c r="B7" t="n">
         <v>57975</v>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469459</v>
+        <v>469334</v>
       </c>
       <c r="R7" t="n">
-        <v>7034328</v>
+        <v>7034384</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1282,7 +1282,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134215430</v>
+        <v>134215428</v>
       </c>
       <c r="B8" t="n">
         <v>57975</v>
@@ -1320,7 +1320,7 @@
         <v>469308</v>
       </c>
       <c r="R8" t="n">
-        <v>7034390</v>
+        <v>7034375</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1384,7 +1384,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134215434</v>
+        <v>134215430</v>
       </c>
       <c r="B9" t="n">
         <v>57975</v>
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>469220</v>
+        <v>469308</v>
       </c>
       <c r="R9" t="n">
-        <v>7034371</v>
+        <v>7034390</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1486,7 +1486,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134215428</v>
+        <v>134215431</v>
       </c>
       <c r="B10" t="n">
         <v>57975</v>
@@ -1521,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>469308</v>
+        <v>469217</v>
       </c>
       <c r="R10" t="n">
-        <v>7034375</v>
+        <v>7034380</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1588,7 +1588,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134215423</v>
+        <v>134215433</v>
       </c>
       <c r="B11" t="n">
         <v>57975</v>
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>469386</v>
+        <v>469220</v>
       </c>
       <c r="R11" t="n">
-        <v>7034241</v>
+        <v>7034360</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1690,7 +1690,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134215427</v>
+        <v>134215434</v>
       </c>
       <c r="B12" t="n">
         <v>57975</v>
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>469334</v>
+        <v>469220</v>
       </c>
       <c r="R12" t="n">
-        <v>7034384</v>
+        <v>7034371</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 57857-2025 artfynd.xlsx
+++ b/artfynd/A 57857-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215444</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215423</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215424</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215425</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215426</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215427</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,6 +1416,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215428</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1483,6 +1523,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215430</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1585,6 +1630,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215431</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1687,6 +1737,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215433</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1789,8 +1844,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215434</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>